--- a/NuRePrCalc/ExcelDB.xlsx
+++ b/NuRePrCalc/ExcelDB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kursovaya\NuRePrCalc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kursovaya\Kursach\NuRePrCalc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D46782-AA5D-4A76-8CB0-8995E8584C5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B304D7E-6C5D-48AB-AE85-60608C08EE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12315" yWindow="1740" windowWidth="16065" windowHeight="12615" xr2:uid="{1CCBBA1E-2000-48FF-870F-B726FE87704F}"/>
+    <workbookView xWindow="7605" yWindow="2055" windowWidth="16065" windowHeight="12615" xr2:uid="{1CCBBA1E-2000-48FF-870F-B726FE87704F}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист2" sheetId="2" r:id="rId1"/>
@@ -1724,34 +1724,34 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>2.3195000000000001E-5</c:v>
+                  <c:v>2.0948E-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.4652999999999995E-5</c:v>
+                  <c:v>3.1482000000000001E-5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.8263999999999997E-5</c:v>
+                  <c:v>4.3959000000000004E-5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.3237999999999993E-5</c:v>
+                  <c:v>5.7715000000000006E-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.929100000000001E-5</c:v>
+                  <c:v>7.2508000000000004E-5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9.6501999999999992E-5</c:v>
+                  <c:v>8.8374999999999993E-5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.1509699999999999E-4</c:v>
+                  <c:v>1.0552099999999999E-4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.3480799999999999E-4</c:v>
+                  <c:v>1.2369899999999998E-4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.5546099999999999E-4</c:v>
+                  <c:v>1.4275599999999999E-4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.7703E-4</c:v>
+                  <c:v>1.6251899999999999E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2174,34 +2174,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.69593999999999989</c:v>
+                  <c:v>0.70665</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.67890000000000006</c:v>
+                  <c:v>0.6915</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.68353999999999993</c:v>
+                  <c:v>0.69382999999999995</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.6839599999999999</c:v>
+                  <c:v>0.69298999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.68269000000000002</c:v>
+                  <c:v>0.68101000000000012</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.68815999999999999</c:v>
+                  <c:v>0.68459000000000003</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.68998999999999999</c:v>
+                  <c:v>0.69125000000000003</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.70320000000000005</c:v>
+                  <c:v>0.70466999999999991</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.71534999999999993</c:v>
+                  <c:v>0.71850000000000003</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.72575999999999996</c:v>
+                  <c:v>0.73038000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2589,34 +2589,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>3.2485E-2</c:v>
+                  <c:v>3.0279999999999994E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.9928000000000005E-2</c:v>
+                  <c:v>3.7723000000000007E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.6892000000000003E-2</c:v>
+                  <c:v>4.4791999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.3576999999999993E-2</c:v>
+                  <c:v>5.1623999999999996E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.9741000000000002E-2</c:v>
+                  <c:v>5.8061000000000008E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.5325999999999995E-2</c:v>
+                  <c:v>6.4233999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.0473999999999995E-2</c:v>
+                  <c:v>6.9654999999999995E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.5205999999999995E-2</c:v>
+                  <c:v>7.4975E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>7.9422000000000006E-2</c:v>
+                  <c:v>7.9905000000000004E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8.3222000000000004E-2</c:v>
+                  <c:v>8.4524000000000002E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3012,34 +3012,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.0183949999999999</c:v>
+                  <c:v>0.99094800000000005</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.80281199999999997</c:v>
+                  <c:v>0.78120299999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.66261300000000001</c:v>
+                  <c:v>0.64478400000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.56413800000000003</c:v>
+                  <c:v>0.54895500000000008</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.49119099999999999</c:v>
+                  <c:v>0.47796099999999997</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.43520300000000001</c:v>
+                  <c:v>0.42350599999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.39042099999999996</c:v>
+                  <c:v>0.37992100000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.353987</c:v>
+                  <c:v>0.34495700000000001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.32380599999999998</c:v>
+                  <c:v>0.31551099999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.29837799999999998</c:v>
+                  <c:v>0.29069200000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3443,34 +3443,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.310038</c:v>
+                  <c:v>1.3914550000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.328606</c:v>
+                  <c:v>1.4235469999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.3466079999999998</c:v>
+                  <c:v>1.4529939999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.3655299999999999</c:v>
+                  <c:v>1.4814919999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.384182</c:v>
+                  <c:v>1.5103289999999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.401764</c:v>
+                  <c:v>1.532867</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.4185610000000002</c:v>
+                  <c:v>1.5558800000000002</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.4334779999999998</c:v>
+                  <c:v>1.57653</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.447721</c:v>
+                  <c:v>1.5957080000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.4606159999999999</c:v>
+                  <c:v>1.6130760000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7160,13 +7160,13 @@
         <v>500</v>
       </c>
       <c r="B3" s="75">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C3" s="75">
         <v>0</v>
       </c>
       <c r="D3" s="75">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="E3" s="75">
         <v>21</v>
@@ -7179,15 +7179,15 @@
       </c>
       <c r="H3" s="77">
         <f>F100</f>
-        <v>1.3842425757575756</v>
+        <v>1.5086125939393935</v>
       </c>
       <c r="I3" s="77">
         <f>F81</f>
-        <v>0.4924982</v>
+        <v>0.479275709090909</v>
       </c>
       <c r="J3" s="77">
         <f>F62</f>
-        <v>5.9672248484848492E-2</v>
+        <v>5.8039084848484856E-2</v>
       </c>
       <c r="K3" s="76">
         <v>90</v>
@@ -7308,32 +7308,32 @@
     <row r="8" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="79">
         <f>F25</f>
-        <v>7.930247878787879E-5</v>
+        <v>7.2539587878787877E-5</v>
       </c>
       <c r="B8" s="80">
         <f>F43</f>
-        <v>0.68261530536130521</v>
+        <v>0.68552113752913768</v>
       </c>
       <c r="C8" s="81">
         <f>F3*G3/A8</f>
-        <v>12609.946312962513</v>
+        <v>13785.575976403105</v>
       </c>
       <c r="D8" s="82">
         <f>IF($C$8&gt;1000,0.4*M3*C8^0.6*B8^0.36,0.56*M3*C8^0.5*B8^0.36)</f>
-        <v>100.64479084235037</v>
+        <v>106.33652093225422</v>
       </c>
       <c r="E8" s="82">
         <f>IF(C8&gt;1000,0.22*M3*C8^0.65*B8^0.36,0.56*M3*C8^0.5*B8^0.36)</f>
-        <v>88.754351078959459</v>
+        <v>94.192512718244089</v>
       </c>
       <c r="F8" s="70"/>
       <c r="G8" s="68">
         <f>D8*$J$3/$G$3</f>
-        <v>60.057009678503356</v>
+        <v>61.716743608797884</v>
       </c>
       <c r="H8" s="68">
         <f>E8*$J$3/$G$3</f>
-        <v>52.961716916951488</v>
+        <v>54.668472377461569</v>
       </c>
       <c r="I8" s="6"/>
     </row>
@@ -7393,7 +7393,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="18">
         <f>B3</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H11" s="19">
         <f>C3</f>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="I11" s="19">
         <f>D3</f>
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="J11" s="20">
         <f>E3</f>
@@ -7434,7 +7434,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="26">
         <f t="shared" ref="G12:G21" si="0">$G$11*B12/100</f>
-        <v>0</v>
+        <v>2.6459999999999997E-6</v>
       </c>
       <c r="H12" s="24">
         <f t="shared" ref="H12:H21" si="1">$H$11*C12/100</f>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="I12" s="24">
         <f t="shared" ref="I12:I21" si="2">$I$11*D12/100</f>
-        <v>1.8407000000000002E-5</v>
+        <v>1.3514E-5</v>
       </c>
       <c r="J12" s="25">
         <f t="shared" ref="J12:J21" si="3">$J$11*E12/100</f>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="K12" s="27">
         <f t="shared" ref="K12:K21" si="4">SUM(G12:J12)</f>
-        <v>2.3195000000000001E-5</v>
+        <v>2.0948E-5</v>
       </c>
       <c r="N12">
         <v>10</v>
@@ -7461,19 +7461,19 @@
       </c>
       <c r="P12">
         <f>IF($C$8&gt;1000,0.4*O12*$C$8^0.6*$B$8^0.36,0.56*O12*$C$8^0.5*$B$8^0.36)</f>
-        <v>42.270812153787155</v>
+        <v>44.661338791546775</v>
       </c>
       <c r="Q12">
         <f>IF($C$8&gt;1000,0.22*O12*$C$8^0.65*$B$8^0.36,0.56*O12*$C$8^0.5*$B$8^0.36)</f>
-        <v>37.276827453162966</v>
+        <v>39.560855341662517</v>
       </c>
       <c r="R12" s="71">
         <f>P12*$J$3/$G$3</f>
-        <v>25.223944064971406</v>
+        <v>25.921032315695111</v>
       </c>
       <c r="S12" s="71">
         <f>Q12*$J$3/$G$3</f>
-        <v>22.243921105119625</v>
+        <v>22.960758398533859</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7499,7 +7499,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="26">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.1369999999999995E-6</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="1"/>
@@ -7507,7 +7507,7 @@
       </c>
       <c r="I13" s="8">
         <f t="shared" si="2"/>
-        <v>2.7491999999999997E-5</v>
+        <v>2.0184000000000002E-5</v>
       </c>
       <c r="J13" s="30">
         <f t="shared" si="3"/>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="K13" s="31">
         <f t="shared" si="4"/>
-        <v>3.4652999999999995E-5</v>
+        <v>3.1482000000000001E-5</v>
       </c>
       <c r="N13">
         <v>20</v>
@@ -7526,19 +7526,19 @@
       </c>
       <c r="P13">
         <f t="shared" ref="P13:P20" si="6">IF($C$8&gt;1000,0.4*O13*$C$8^0.6*$B$8^0.36,0.56*O13*$C$8^0.5*$B$8^0.36)</f>
-        <v>52.335291238022194</v>
+        <v>55.294990884772197</v>
       </c>
       <c r="Q13">
         <f t="shared" ref="Q13:Q20" si="7">IF($C$8&gt;1000,0.22*O13*$C$8^0.65*$B$8^0.36,0.56*O13*$C$8^0.5*$B$8^0.36)</f>
-        <v>46.152262561058912</v>
+        <v>48.980106613486932</v>
       </c>
       <c r="R13" s="71">
         <f t="shared" ref="R13:R20" si="8">P13*$J$3/$G$3</f>
-        <v>31.22964503282174</v>
+        <v>32.092706676574899</v>
       </c>
       <c r="S13" s="71">
         <f t="shared" ref="S13:S20" si="9">Q13*$J$3/$G$3</f>
-        <v>27.540092796814772</v>
+        <v>28.42760563628002</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7564,7 +7564,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="26">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5.9009999999999999E-6</v>
       </c>
       <c r="H14" s="8">
         <f t="shared" si="1"/>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="I14" s="8">
         <f t="shared" si="2"/>
-        <v>3.8393999999999999E-5</v>
+        <v>2.8188000000000002E-5</v>
       </c>
       <c r="J14" s="30">
         <f t="shared" si="3"/>
@@ -7580,7 +7580,7 @@
       </c>
       <c r="K14" s="31">
         <f t="shared" si="4"/>
-        <v>4.8263999999999997E-5</v>
+        <v>4.3959000000000004E-5</v>
       </c>
       <c r="N14">
         <v>30</v>
@@ -7591,19 +7591,19 @@
       </c>
       <c r="P14">
         <f t="shared" si="6"/>
-        <v>67.432009864374749</v>
+        <v>71.24546902461033</v>
       </c>
       <c r="Q14">
         <f t="shared" si="7"/>
-        <v>59.465415222902827</v>
+        <v>63.108983521223543</v>
       </c>
       <c r="R14" s="71">
         <f t="shared" si="8"/>
-        <v>40.238196484597246</v>
+        <v>41.350218217894586</v>
       </c>
       <c r="S14" s="71">
         <f t="shared" si="9"/>
-        <v>35.484350334357494</v>
+        <v>36.627876492899254</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7629,7 +7629,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="26">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7.8539999999999997E-6</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="1"/>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="I15" s="8">
         <f t="shared" si="2"/>
-        <v>5.0322999999999999E-5</v>
+        <v>3.6946000000000002E-5</v>
       </c>
       <c r="J15" s="30">
         <f t="shared" si="3"/>
@@ -7645,7 +7645,7 @@
       </c>
       <c r="K15" s="31">
         <f t="shared" si="4"/>
-        <v>6.3237999999999993E-5</v>
+        <v>5.7715000000000006E-5</v>
       </c>
       <c r="N15">
         <v>40</v>
@@ -7656,19 +7656,19 @@
       </c>
       <c r="P15">
         <f t="shared" si="6"/>
-        <v>78.502936857033305</v>
+        <v>82.942486327158306</v>
       </c>
       <c r="Q15">
         <f t="shared" si="7"/>
-        <v>69.228393841588371</v>
+        <v>73.470159920230387</v>
       </c>
       <c r="R15" s="71">
         <f t="shared" si="8"/>
-        <v>46.844467549232618</v>
+        <v>48.139060014862359</v>
       </c>
       <c r="S15" s="71">
         <f t="shared" si="9"/>
-        <v>41.310139195222156</v>
+        <v>42.641408454420024</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7694,7 +7694,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="26">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9.9960000000000005E-6</v>
       </c>
       <c r="H16" s="8">
         <f t="shared" si="1"/>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="I16" s="8">
         <f t="shared" si="2"/>
-        <v>6.3121000000000008E-5</v>
+        <v>4.6342000000000005E-5</v>
       </c>
       <c r="J16" s="30">
         <f t="shared" si="3"/>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="K16" s="31">
         <f t="shared" si="4"/>
-        <v>7.929100000000001E-5</v>
+        <v>7.2508000000000004E-5</v>
       </c>
       <c r="N16">
         <v>50</v>
@@ -7721,19 +7721,19 @@
       </c>
       <c r="P16">
         <f t="shared" si="6"/>
-        <v>88.567415941268337</v>
+        <v>93.576138420383728</v>
       </c>
       <c r="Q16">
         <f t="shared" si="7"/>
-        <v>78.10382894948431</v>
+        <v>82.889411192054794</v>
       </c>
       <c r="R16" s="71">
         <f t="shared" si="8"/>
-        <v>52.850168517082956</v>
+        <v>54.310734375742143</v>
       </c>
       <c r="S16" s="71">
         <f t="shared" si="9"/>
-        <v>46.606310886917306</v>
+        <v>48.108255692166182</v>
       </c>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7759,7 +7759,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="26">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.2306E-5</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="1"/>
@@ -7767,7 +7767,7 @@
       </c>
       <c r="I17" s="8">
         <f t="shared" si="2"/>
-        <v>7.6866999999999994E-5</v>
+        <v>5.6433999999999995E-5</v>
       </c>
       <c r="J17" s="30">
         <f t="shared" si="3"/>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="K17" s="31">
         <f t="shared" si="4"/>
-        <v>9.6501999999999992E-5</v>
+        <v>8.8374999999999993E-5</v>
       </c>
       <c r="N17">
         <v>60</v>
@@ -7786,19 +7786,19 @@
       </c>
       <c r="P17">
         <f t="shared" si="6"/>
-        <v>94.606103391809341</v>
+        <v>99.956329676318973</v>
       </c>
       <c r="Q17">
         <f t="shared" si="7"/>
-        <v>83.429090014221885</v>
+        <v>88.540961955149442</v>
       </c>
       <c r="R17" s="71">
         <f t="shared" si="8"/>
-        <v>56.453589097793149</v>
+        <v>58.013738992270021</v>
       </c>
       <c r="S17" s="71">
         <f t="shared" si="9"/>
-        <v>49.784013901934401</v>
+        <v>51.388364034813883</v>
       </c>
     </row>
     <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7824,7 +7824,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="26">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.4784000000000001E-5</v>
       </c>
       <c r="H18" s="8">
         <f t="shared" si="1"/>
@@ -7832,7 +7832,7 @@
       </c>
       <c r="I18" s="8">
         <f t="shared" si="2"/>
-        <v>9.1639999999999997E-5</v>
+        <v>6.7279999999999993E-5</v>
       </c>
       <c r="J18" s="30">
         <f t="shared" si="3"/>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="K18" s="31">
         <f t="shared" si="4"/>
-        <v>1.1509699999999999E-4</v>
+        <v>1.0552099999999999E-4</v>
       </c>
       <c r="N18">
         <v>70</v>
@@ -7851,19 +7851,19 @@
       </c>
       <c r="P18">
         <f t="shared" si="6"/>
-        <v>98.631895025503368</v>
+        <v>104.20979051360914</v>
       </c>
       <c r="Q18">
         <f t="shared" si="7"/>
-        <v>86.979264057380249</v>
+        <v>92.308662463879202</v>
       </c>
       <c r="R18" s="71">
         <f t="shared" si="8"/>
-        <v>58.855869484933287</v>
+        <v>60.482408736621927</v>
       </c>
       <c r="S18" s="71">
         <f t="shared" si="9"/>
-        <v>51.902482578612457</v>
+        <v>53.57510292991234</v>
       </c>
     </row>
     <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7889,7 +7889,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="26">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7430000000000001E-5</v>
       </c>
       <c r="H19" s="8">
         <f t="shared" si="1"/>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="I19" s="8">
         <f t="shared" si="2"/>
-        <v>1.07361E-4</v>
+        <v>7.8821999999999985E-5</v>
       </c>
       <c r="J19" s="30">
         <f t="shared" si="3"/>
@@ -7905,7 +7905,7 @@
       </c>
       <c r="K19" s="31">
         <f t="shared" si="4"/>
-        <v>1.3480799999999999E-4</v>
+        <v>1.2369899999999998E-4</v>
       </c>
       <c r="N19">
         <v>80</v>
@@ -7916,19 +7916,19 @@
       </c>
       <c r="P19">
         <f t="shared" si="6"/>
-        <v>100.64479084235037</v>
+        <v>106.33652093225422</v>
       </c>
       <c r="Q19">
         <f t="shared" si="7"/>
-        <v>88.754351078959459</v>
+        <v>94.192512718244089</v>
       </c>
       <c r="R19" s="71">
         <f t="shared" si="8"/>
-        <v>60.057009678503356</v>
+        <v>61.716743608797884</v>
       </c>
       <c r="S19" s="71">
         <f t="shared" si="9"/>
-        <v>52.961716916951488</v>
+        <v>54.668472377461569</v>
       </c>
     </row>
     <row r="20" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7954,7 +7954,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="26">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.0201999999999997E-5</v>
       </c>
       <c r="H20" s="8">
         <f t="shared" si="1"/>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="I20" s="8">
         <f t="shared" si="2"/>
-        <v>1.23793E-4</v>
+        <v>9.0885999999999983E-5</v>
       </c>
       <c r="J20" s="30">
         <f t="shared" si="3"/>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="K20" s="31">
         <f t="shared" si="4"/>
-        <v>1.5546099999999999E-4</v>
+        <v>1.4275599999999999E-4</v>
       </c>
       <c r="N20">
         <v>90</v>
@@ -7981,19 +7981,19 @@
       </c>
       <c r="P20">
         <f t="shared" si="6"/>
-        <v>100.64479084235037</v>
+        <v>106.33652093225422</v>
       </c>
       <c r="Q20">
         <f t="shared" si="7"/>
-        <v>88.754351078959459</v>
+        <v>94.192512718244089</v>
       </c>
       <c r="R20" s="71">
         <f t="shared" si="8"/>
-        <v>60.057009678503356</v>
+        <v>61.716743608797884</v>
       </c>
       <c r="S20" s="71">
         <f t="shared" si="9"/>
-        <v>52.961716916951488</v>
+        <v>54.668472377461569</v>
       </c>
     </row>
     <row r="21" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8019,7 +8019,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.2974000000000001E-5</v>
       </c>
       <c r="H21" s="34">
         <f t="shared" si="1"/>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="I21" s="34">
         <f t="shared" si="2"/>
-        <v>1.41015E-4</v>
+        <v>1.0352999999999999E-4</v>
       </c>
       <c r="J21" s="35">
         <f t="shared" si="3"/>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="K21" s="36">
         <f t="shared" si="4"/>
-        <v>1.7703E-4</v>
+        <v>1.6251899999999999E-4</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.25">
@@ -8087,21 +8087,21 @@
     <row r="25" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" cm="1">
         <f t="array" ref="A25">INDEX(LINEST(K12:K21,A12:A21^{1,2}),1,1)</f>
-        <v>6.0730681818181772E-11</v>
+        <v>5.6204545454545418E-11</v>
       </c>
       <c r="B25" s="8" cm="1">
         <f t="array" ref="B25">INDEX(LINEST(K12:K21,A12:A21^{1,2}),1,2)</f>
-        <v>1.0505558333333337E-7</v>
+        <v>9.6419969696969711E-8</v>
       </c>
       <c r="C25" s="8" cm="1">
         <f t="array" ref="C25">INDEX(LINEST(K12:K21,A12:A21^{1,2}),1,3)</f>
-        <v>1.1592016666666657E-5</v>
+        <v>1.0278466666666663E-5</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="6"/>
       <c r="F25" s="103">
         <f>$A$25*$A$3^2+$B$25*$A$3+$C$25</f>
-        <v>7.930247878787879E-5</v>
+        <v>7.2539587878787877E-5</v>
       </c>
       <c r="G25" s="104"/>
       <c r="H25" s="105"/>
@@ -8178,7 +8178,7 @@
       <c r="F29" s="6"/>
       <c r="G29" s="18">
         <f>B3</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H29" s="19">
         <f>C3</f>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="I29" s="19">
         <f>D3</f>
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="J29" s="20">
         <f>E3</f>
@@ -8215,7 +8215,7 @@
       <c r="F30" s="6"/>
       <c r="G30" s="26">
         <f t="shared" ref="G30:G39" si="10">G$29*B30/100</f>
-        <v>0</v>
+        <v>0.15624000000000002</v>
       </c>
       <c r="H30" s="26">
         <f t="shared" ref="H30:H39" si="11">H$29*C30/100</f>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="I30" s="26">
         <f t="shared" ref="I30:I39" si="12">I$29*D30/100</f>
-        <v>0.5474699999999999</v>
+        <v>0.40193999999999996</v>
       </c>
       <c r="J30" s="41">
         <f t="shared" ref="J30:J39" si="13">J$29*E30/100</f>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="K30" s="41">
         <f t="shared" ref="K30:K39" si="14">SUM(G30:J30)</f>
-        <v>0.69593999999999989</v>
+        <v>0.70665</v>
       </c>
     </row>
     <row r="31" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8253,7 +8253,7 @@
       <c r="F31" s="6"/>
       <c r="G31" s="26">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.15561</v>
       </c>
       <c r="H31" s="26">
         <f t="shared" si="11"/>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="I31" s="26">
         <f t="shared" si="12"/>
-        <v>0.53799000000000008</v>
+        <v>0.39498000000000005</v>
       </c>
       <c r="J31" s="41">
         <f t="shared" si="13"/>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="K31" s="44">
         <f t="shared" si="14"/>
-        <v>0.67890000000000006</v>
+        <v>0.6915</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8291,7 +8291,7 @@
       <c r="F32" s="6"/>
       <c r="G32" s="26">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.15498000000000001</v>
       </c>
       <c r="H32" s="26">
         <f t="shared" si="11"/>
@@ -8299,7 +8299,7 @@
       </c>
       <c r="I32" s="26">
         <f t="shared" si="12"/>
-        <v>0.54430999999999996</v>
+        <v>0.39961999999999998</v>
       </c>
       <c r="J32" s="41">
         <f t="shared" si="13"/>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="K32" s="44">
         <f t="shared" si="14"/>
-        <v>0.68353999999999993</v>
+        <v>0.69382999999999995</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8329,7 +8329,7 @@
       <c r="F33" s="6"/>
       <c r="G33" s="26">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.15372</v>
       </c>
       <c r="H33" s="26">
         <f t="shared" si="11"/>
@@ -8337,7 +8337,7 @@
       </c>
       <c r="I33" s="26">
         <f t="shared" si="12"/>
-        <v>0.54430999999999996</v>
+        <v>0.39961999999999998</v>
       </c>
       <c r="J33" s="41">
         <f t="shared" si="13"/>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="K33" s="44">
         <f t="shared" si="14"/>
-        <v>0.6839599999999999</v>
+        <v>0.69298999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8367,7 +8367,7 @@
       <c r="F34" s="6"/>
       <c r="G34" s="26">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.14217000000000002</v>
       </c>
       <c r="H34" s="26">
         <f t="shared" si="11"/>
@@ -8375,7 +8375,7 @@
       </c>
       <c r="I34" s="26">
         <f t="shared" si="12"/>
-        <v>0.54115000000000002</v>
+        <v>0.39730000000000004</v>
       </c>
       <c r="J34" s="41">
         <f t="shared" si="13"/>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="K34" s="44">
         <f t="shared" si="14"/>
-        <v>0.68269000000000002</v>
+        <v>0.68101000000000012</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8405,7 +8405,7 @@
       <c r="F35" s="6"/>
       <c r="G35" s="26">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.14112</v>
       </c>
       <c r="H35" s="26">
         <f t="shared" si="11"/>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="I35" s="26">
         <f t="shared" si="12"/>
-        <v>0.54430999999999996</v>
+        <v>0.39961999999999998</v>
       </c>
       <c r="J35" s="41">
         <f t="shared" si="13"/>
@@ -8421,7 +8421,7 @@
       </c>
       <c r="K35" s="44">
         <f t="shared" si="14"/>
-        <v>0.68815999999999999</v>
+        <v>0.68459000000000003</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8443,7 +8443,7 @@
       <c r="F36" s="6"/>
       <c r="G36" s="26">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.14531999999999998</v>
       </c>
       <c r="H36" s="26">
         <f t="shared" si="11"/>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="I36" s="26">
         <f t="shared" si="12"/>
-        <v>0.54193999999999998</v>
+        <v>0.39788000000000001</v>
       </c>
       <c r="J36" s="41">
         <f t="shared" si="13"/>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="K36" s="44">
         <f t="shared" si="14"/>
-        <v>0.68998999999999999</v>
+        <v>0.69125000000000003</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8481,7 +8481,7 @@
       <c r="F37" s="6"/>
       <c r="G37" s="26">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.14825999999999998</v>
       </c>
       <c r="H37" s="26">
         <f t="shared" si="11"/>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I37" s="26">
         <f t="shared" si="12"/>
-        <v>0.55220999999999998</v>
+        <v>0.40541999999999995</v>
       </c>
       <c r="J37" s="41">
         <f t="shared" si="13"/>
@@ -8497,7 +8497,7 @@
       </c>
       <c r="K37" s="44">
         <f t="shared" si="14"/>
-        <v>0.70320000000000005</v>
+        <v>0.70466999999999991</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8519,7 +8519,7 @@
       <c r="F38" s="6"/>
       <c r="G38" s="26">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.15182999999999999</v>
       </c>
       <c r="H38" s="26">
         <f t="shared" si="11"/>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="I38" s="26">
         <f t="shared" si="12"/>
-        <v>0.55931999999999993</v>
+        <v>0.41064000000000001</v>
       </c>
       <c r="J38" s="41">
         <f t="shared" si="13"/>
@@ -8535,7 +8535,7 @@
       </c>
       <c r="K38" s="44">
         <f t="shared" si="14"/>
-        <v>0.71534999999999993</v>
+        <v>0.71850000000000003</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8557,7 +8557,7 @@
       <c r="F39" s="6"/>
       <c r="G39" s="12">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.15456</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="11"/>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="I39" s="12">
         <f t="shared" si="12"/>
-        <v>0.56406000000000001</v>
+        <v>0.41411999999999999</v>
       </c>
       <c r="J39" s="21">
         <f t="shared" si="13"/>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="K39" s="49">
         <f t="shared" si="14"/>
-        <v>0.72575999999999996</v>
+        <v>0.73038000000000003</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -8627,24 +8627,24 @@
     <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" cm="1">
         <f t="array" ref="A43">INDEX(LINEST(K30:K39,A30:A39^{1,2,3}),1,1)</f>
-        <v>-3.8564491064491907E-11</v>
+        <v>4.8609168609168391E-11</v>
       </c>
       <c r="B43" s="8" cm="1">
         <f t="array" ref="B43">INDEX(LINEST(K30:K39,A30:A39^{1,2,3}),1,2)</f>
-        <v>1.8738519813519941E-7</v>
+        <v>8.2128205128205446E-8</v>
       </c>
       <c r="C43" s="8" cm="1">
         <f t="array" ref="C43">INDEX(LINEST(K30:K39,A30:A39^{1,2,3}),1,3)</f>
-        <v>-1.2636219891219938E-4</v>
+        <v>-1.139914529914531E-4</v>
       </c>
       <c r="D43" s="8" cm="1">
         <f t="array" ref="D43">INDEX(LINEST(K30:K39,A30:A39^{1,2,3}),1,4)</f>
-        <v>0.70377066666666654</v>
+        <v>0.71590866666666686</v>
       </c>
       <c r="E43" s="6"/>
       <c r="F43" s="103">
         <f>$A$43*A3^3+$B$43*A3^2+$C$43*A3+$D$43</f>
-        <v>0.68261530536130521</v>
+        <v>0.68552113752913768</v>
       </c>
       <c r="G43" s="104"/>
       <c r="H43" s="105"/>
@@ -8733,7 +8733,7 @@
       <c r="F48" s="6"/>
       <c r="G48" s="18">
         <f>B3</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H48" s="19">
         <f>C3</f>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="I48" s="19">
         <f>D3</f>
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="J48" s="20">
         <f>E3</f>
@@ -8774,7 +8774,7 @@
       <c r="F49" s="6"/>
       <c r="G49" s="26">
         <f t="shared" ref="G49:G58" si="15">G$48*B49/100</f>
-        <v>0</v>
+        <v>4.6829999999999997E-3</v>
       </c>
       <c r="H49" s="39">
         <f t="shared" ref="H49:H58" si="16">H$48*C49/100</f>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="I49" s="39">
         <f t="shared" ref="I49:I58" si="17">I$48*D49/100</f>
-        <v>2.5911999999999998E-2</v>
+        <v>1.9023999999999996E-2</v>
       </c>
       <c r="J49" s="40">
         <f t="shared" ref="J49:J58" si="18">J$48*E49/100</f>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="K49" s="41">
         <f t="shared" ref="K49:K58" si="19">SUM(G49:J49)</f>
-        <v>3.2485E-2</v>
+        <v>3.0279999999999994E-2</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8816,7 +8816,7 @@
       <c r="F50" s="6"/>
       <c r="G50" s="26">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>6.3210000000000002E-3</v>
       </c>
       <c r="H50" s="39">
         <f t="shared" si="16"/>
@@ -8824,7 +8824,7 @@
       </c>
       <c r="I50" s="39">
         <f t="shared" si="17"/>
-        <v>3.2074000000000005E-2</v>
+        <v>2.3548000000000003E-2</v>
       </c>
       <c r="J50" s="40">
         <f t="shared" si="18"/>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="K50" s="44">
         <f t="shared" si="19"/>
-        <v>3.9928000000000005E-2</v>
+        <v>3.7723000000000007E-2</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8858,7 +8858,7 @@
       <c r="F51" s="6"/>
       <c r="G51" s="26">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>7.9589999999999991E-3</v>
       </c>
       <c r="H51" s="39">
         <f t="shared" si="16"/>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="I51" s="39">
         <f t="shared" si="17"/>
-        <v>3.7841E-2</v>
+        <v>2.7782000000000001E-2</v>
       </c>
       <c r="J51" s="40">
         <f t="shared" si="18"/>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="K51" s="44">
         <f t="shared" si="19"/>
-        <v>4.6892000000000003E-2</v>
+        <v>4.4791999999999998E-2</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8900,7 +8900,7 @@
       <c r="F52" s="6"/>
       <c r="G52" s="26">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>9.5759999999999994E-3</v>
       </c>
       <c r="H52" s="39">
         <f t="shared" si="16"/>
@@ -8908,7 +8908,7 @@
       </c>
       <c r="I52" s="39">
         <f t="shared" si="17"/>
-        <v>4.3370999999999993E-2</v>
+        <v>3.1841999999999995E-2</v>
       </c>
       <c r="J52" s="40">
         <f t="shared" si="18"/>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="K52" s="44">
         <f t="shared" si="19"/>
-        <v>5.3576999999999993E-2</v>
+        <v>5.1623999999999996E-2</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8942,7 +8942,7 @@
       <c r="F53" s="6"/>
       <c r="G53" s="26">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1.1214E-2</v>
       </c>
       <c r="H53" s="39">
         <f t="shared" si="16"/>
@@ -8950,7 +8950,7 @@
       </c>
       <c r="I53" s="39">
         <f t="shared" si="17"/>
-        <v>4.8506000000000001E-2</v>
+        <v>3.5612000000000005E-2</v>
       </c>
       <c r="J53" s="40">
         <f t="shared" si="18"/>
@@ -8958,7 +8958,7 @@
       </c>
       <c r="K53" s="44">
         <f t="shared" si="19"/>
-        <v>5.9741000000000002E-2</v>
+        <v>5.8061000000000008E-2</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8984,7 +8984,7 @@
       <c r="F54" s="6"/>
       <c r="G54" s="26">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1.3041000000000001E-2</v>
       </c>
       <c r="H54" s="39">
         <f t="shared" si="16"/>
@@ -8992,7 +8992,7 @@
       </c>
       <c r="I54" s="39">
         <f t="shared" si="17"/>
-        <v>5.3166999999999999E-2</v>
+        <v>3.9033999999999999E-2</v>
       </c>
       <c r="J54" s="40">
         <f t="shared" si="18"/>
@@ -9000,7 +9000,7 @@
       </c>
       <c r="K54" s="44">
         <f t="shared" si="19"/>
-        <v>6.5325999999999995E-2</v>
+        <v>6.4233999999999999E-2</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9026,7 +9026,7 @@
       <c r="F55" s="6"/>
       <c r="G55" s="26">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1.4448000000000001E-2</v>
       </c>
       <c r="H55" s="39">
         <f t="shared" si="16"/>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="I55" s="39">
         <f t="shared" si="17"/>
-        <v>5.7432999999999998E-2</v>
+        <v>4.2165999999999995E-2</v>
       </c>
       <c r="J55" s="40">
         <f t="shared" si="18"/>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="K55" s="44">
         <f t="shared" si="19"/>
-        <v>7.0473999999999995E-2</v>
+        <v>6.9654999999999995E-2</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9068,7 +9068,7 @@
       <c r="F56" s="6"/>
       <c r="G56" s="26">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1.6064999999999999E-2</v>
       </c>
       <c r="H56" s="39">
         <f t="shared" si="16"/>
@@ -9076,7 +9076,7 @@
       </c>
       <c r="I56" s="39">
         <f t="shared" si="17"/>
-        <v>6.1303999999999997E-2</v>
+        <v>4.5007999999999999E-2</v>
       </c>
       <c r="J56" s="40">
         <f t="shared" si="18"/>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="K56" s="44">
         <f t="shared" si="19"/>
-        <v>7.5205999999999995E-2</v>
+        <v>7.4975E-2</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9110,7 +9110,7 @@
       <c r="F57" s="6"/>
       <c r="G57" s="26">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1.7682000000000003E-2</v>
       </c>
       <c r="H57" s="39">
         <f t="shared" si="16"/>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="I57" s="39">
         <f t="shared" si="17"/>
-        <v>6.4701000000000009E-2</v>
+        <v>4.7502000000000003E-2</v>
       </c>
       <c r="J57" s="40">
         <f t="shared" si="18"/>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="K57" s="44">
         <f t="shared" si="19"/>
-        <v>7.9422000000000006E-2</v>
+        <v>7.9905000000000004E-2</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9152,7 +9152,7 @@
       <c r="F58" s="6"/>
       <c r="G58" s="12">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1.9299E-2</v>
       </c>
       <c r="H58" s="13">
         <f t="shared" si="16"/>
@@ -9160,7 +9160,7 @@
       </c>
       <c r="I58" s="13">
         <f t="shared" si="17"/>
-        <v>6.7702999999999999E-2</v>
+        <v>4.9706E-2</v>
       </c>
       <c r="J58" s="14">
         <f t="shared" si="18"/>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="K58" s="49">
         <f t="shared" si="19"/>
-        <v>8.3222000000000004E-2</v>
+        <v>8.4524000000000002E-2</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -9223,21 +9223,21 @@
     <row r="62" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="8" cm="1">
         <f t="array" ref="A62">INDEX(LINEST(K49:K58,A49:A58^{1,2}),1,1)</f>
-        <v>-2.3324621212121168E-8</v>
+        <v>-1.8448484848484831E-8</v>
       </c>
       <c r="B62" s="8" cm="1">
         <f t="array" ref="B62">INDEX(LINEST(K49:K58,A49:A58^{1,2}),1,2)</f>
-        <v>8.2077507575757528E-5</v>
+        <v>8.0575212121212095E-5</v>
       </c>
       <c r="C62" s="8" cm="1">
         <f t="array" ref="C62">INDEX(LINEST(K49:K58,A49:A58^{1,2}),1,3)</f>
-        <v>2.4464650000000018E-2</v>
+        <v>2.2363600000000018E-2</v>
       </c>
       <c r="D62" s="9"/>
       <c r="E62" s="6"/>
       <c r="F62" s="92">
         <f>$A$62*$A$3^2+$B$62*$A$3+$C$62</f>
-        <v>5.9672248484848492E-2</v>
+        <v>5.8039084848484856E-2</v>
       </c>
       <c r="G62" s="93"/>
       <c r="H62" s="94"/>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="G67" s="18">
         <f>B3</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H67" s="19">
         <f>C3</f>
@@ -9295,7 +9295,7 @@
       </c>
       <c r="I67" s="19">
         <f>D3</f>
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="J67" s="20">
         <f>E3</f>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="G68" s="26">
         <f t="shared" ref="G68:G77" si="20">G$48*B68/100</f>
-        <v>0</v>
+        <v>0.19217100000000001</v>
       </c>
       <c r="H68" s="39">
         <f t="shared" ref="H68:H77" si="21">H$48*C68/100</f>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="I68" s="39">
         <f t="shared" ref="I68:I77" si="22">I$48*D68/100</f>
-        <v>0.82618199999999997</v>
+        <v>0.6065640000000001</v>
       </c>
       <c r="J68" s="40">
         <f t="shared" ref="J68:J77" si="23">J$48*E68/100</f>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="K68" s="41">
         <f t="shared" ref="K68:K77" si="24">SUM(G68:J68)</f>
-        <v>1.0183949999999999</v>
+        <v>0.99094800000000005</v>
       </c>
       <c r="L68" s="61"/>
       <c r="M68" s="61"/>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="G69" s="26">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>0.15151500000000001</v>
       </c>
       <c r="H69" s="39">
         <f t="shared" si="21"/>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="I69" s="39">
         <f t="shared" si="22"/>
-        <v>0.65127599999999997</v>
+        <v>0.47815200000000002</v>
       </c>
       <c r="J69" s="40">
         <f t="shared" si="23"/>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="K69" s="44">
         <f t="shared" si="24"/>
-        <v>0.80281199999999997</v>
+        <v>0.78120299999999998</v>
       </c>
       <c r="L69" s="61"/>
       <c r="M69" s="61"/>
@@ -9401,7 +9401,7 @@
       </c>
       <c r="G70" s="26">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>0.12505500000000003</v>
       </c>
       <c r="H70" s="39">
         <f t="shared" si="21"/>
@@ -9409,7 +9409,7 @@
       </c>
       <c r="I70" s="39">
         <f t="shared" si="22"/>
-        <v>0.53751599999999999</v>
+        <v>0.39463199999999998</v>
       </c>
       <c r="J70" s="40">
         <f t="shared" si="23"/>
@@ -9417,7 +9417,7 @@
       </c>
       <c r="K70" s="44">
         <f t="shared" si="24"/>
-        <v>0.66261300000000001</v>
+        <v>0.64478400000000002</v>
       </c>
       <c r="L70" s="61"/>
       <c r="M70" s="61"/>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G71" s="26">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>0.10647000000000001</v>
       </c>
       <c r="H71" s="39">
         <f t="shared" si="21"/>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="I71" s="39">
         <f t="shared" si="22"/>
-        <v>0.45764700000000003</v>
+        <v>0.33599400000000001</v>
       </c>
       <c r="J71" s="40">
         <f t="shared" si="23"/>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="K71" s="44">
         <f t="shared" si="24"/>
-        <v>0.56413800000000003</v>
+        <v>0.54895500000000008</v>
       </c>
       <c r="L71" s="61"/>
       <c r="M71" s="61"/>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="G72" s="26">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>9.2694000000000012E-2</v>
       </c>
       <c r="H72" s="39">
         <f t="shared" si="21"/>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="I72" s="39">
         <f t="shared" si="22"/>
-        <v>0.398476</v>
+        <v>0.29255199999999998</v>
       </c>
       <c r="J72" s="40">
         <f t="shared" si="23"/>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="K72" s="44">
         <f t="shared" si="24"/>
-        <v>0.49119099999999999</v>
+        <v>0.47796099999999997</v>
       </c>
       <c r="L72" s="61"/>
       <c r="M72" s="61"/>
@@ -9518,7 +9518,7 @@
       </c>
       <c r="G73" s="26">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>8.2151999999999989E-2</v>
       </c>
       <c r="H73" s="39">
         <f t="shared" si="21"/>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="I73" s="39">
         <f t="shared" si="22"/>
-        <v>0.353051</v>
+        <v>0.25920199999999999</v>
       </c>
       <c r="J73" s="40">
         <f t="shared" si="23"/>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="K73" s="44">
         <f t="shared" si="24"/>
-        <v>0.43520300000000001</v>
+        <v>0.42350599999999999</v>
       </c>
       <c r="L73" s="61"/>
       <c r="M73" s="61"/>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="G74" s="26">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>7.3689000000000004E-2</v>
       </c>
       <c r="H74" s="39">
         <f t="shared" si="21"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="I74" s="39">
         <f t="shared" si="22"/>
-        <v>0.31671099999999996</v>
+        <v>0.23252199999999998</v>
       </c>
       <c r="J74" s="40">
         <f t="shared" si="23"/>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="K74" s="44">
         <f t="shared" si="24"/>
-        <v>0.39042099999999996</v>
+        <v>0.37992100000000001</v>
       </c>
       <c r="L74" s="61"/>
       <c r="M74" s="61"/>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="G75" s="26">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>6.7305000000000004E-2</v>
       </c>
       <c r="H75" s="39">
         <f t="shared" si="21"/>
@@ -9604,7 +9604,7 @@
       </c>
       <c r="I75" s="39">
         <f t="shared" si="22"/>
-        <v>0.287165</v>
+        <v>0.21082999999999999</v>
       </c>
       <c r="J75" s="40">
         <f t="shared" si="23"/>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="K75" s="44">
         <f t="shared" si="24"/>
-        <v>0.353987</v>
+        <v>0.34495700000000001</v>
       </c>
       <c r="L75" s="61"/>
       <c r="M75" s="61"/>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="G76" s="26">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>6.1529999999999994E-2</v>
       </c>
       <c r="H76" s="39">
         <f t="shared" si="21"/>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="I76" s="39">
         <f t="shared" si="22"/>
-        <v>0.26267499999999999</v>
+        <v>0.19284999999999999</v>
       </c>
       <c r="J76" s="40">
         <f t="shared" si="23"/>
@@ -9651,7 +9651,7 @@
       </c>
       <c r="K76" s="44">
         <f t="shared" si="24"/>
-        <v>0.32380599999999998</v>
+        <v>0.31551099999999999</v>
       </c>
       <c r="L76" s="61"/>
       <c r="M76" s="61"/>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="G77" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>5.6658E-2</v>
       </c>
       <c r="H77" s="13">
         <f t="shared" si="21"/>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="I77" s="13">
         <f t="shared" si="22"/>
-        <v>0.24205599999999999</v>
+        <v>0.17771200000000001</v>
       </c>
       <c r="J77" s="14">
         <f t="shared" si="23"/>
@@ -9690,7 +9690,7 @@
       </c>
       <c r="K77" s="49">
         <f t="shared" si="24"/>
-        <v>0.29837799999999998</v>
+        <v>0.29069200000000001</v>
       </c>
       <c r="L77" s="61"/>
       <c r="M77" s="61"/>
@@ -9742,21 +9742,21 @@
     <row r="81" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8" cm="1">
         <f t="array" ref="A81">INDEX(LINEST(K68:K77,A68:A77^{1,2}),1,1)</f>
-        <v>9.7273522727272726E-7</v>
+        <v>9.4736022727272773E-7</v>
       </c>
       <c r="B81" s="8" cm="1">
         <f t="array" ref="B81">INDEX(LINEST(K68:K77,A68:A77^{1,2}),1,2)</f>
-        <v>-1.7944611136363636E-3</v>
+        <v>-1.7465107954545461E-3</v>
       </c>
       <c r="C81" s="8" cm="1">
         <f t="array" ref="C81">INDEX(LINEST(K68:K77,A68:A77^{1,2}),1,3)</f>
-        <v>1.14654495</v>
+        <v>1.1156910500000001</v>
       </c>
       <c r="D81" s="9"/>
       <c r="E81" s="6"/>
       <c r="F81" s="92">
         <f>$A$81*$A$3^2+$B$81*$A$3+$C$81</f>
-        <v>0.4924982</v>
+        <v>0.479275709090909</v>
       </c>
       <c r="G81" s="93"/>
       <c r="H81" s="94"/>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="G86" s="18">
         <f>B3</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H86" s="19">
         <f>C3</f>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="I86" s="19">
         <f>D3</f>
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="J86" s="20">
         <f>E3</f>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="G87" s="26">
         <f t="shared" ref="G87:G96" si="25">G$48*B87/100</f>
-        <v>0</v>
+        <v>0.35706299999999996</v>
       </c>
       <c r="H87" s="39">
         <f t="shared" ref="H87:H96" si="26">H$48*C87/100</f>
@@ -9846,7 +9846,7 @@
       </c>
       <c r="I87" s="39">
         <f t="shared" ref="I87:I96" si="27">I$48*D87/100</f>
-        <v>1.0369539999999999</v>
+        <v>0.76130799999999998</v>
       </c>
       <c r="J87" s="40">
         <f t="shared" ref="J87:J96" si="28">J$48*E87/100</f>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="K87" s="41">
         <f t="shared" ref="K87:K96" si="29">SUM(G87:J87)</f>
-        <v>1.310038</v>
+        <v>1.3914550000000001</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9875,7 +9875,7 @@
       </c>
       <c r="G88" s="26">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>0.37533300000000003</v>
       </c>
       <c r="H88" s="39">
         <f t="shared" si="26"/>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="I88" s="39">
         <f t="shared" si="27"/>
-        <v>1.054808</v>
+        <v>0.77441599999999999</v>
       </c>
       <c r="J88" s="40">
         <f t="shared" si="28"/>
@@ -9891,7 +9891,7 @@
       </c>
       <c r="K88" s="44">
         <f t="shared" si="29"/>
-        <v>1.328606</v>
+        <v>1.4235469999999999</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9912,7 +9912,7 @@
       </c>
       <c r="G89" s="26">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>0.39116700000000004</v>
       </c>
       <c r="H89" s="39">
         <f t="shared" si="26"/>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="I89" s="39">
         <f t="shared" si="27"/>
-        <v>1.0713189999999999</v>
+        <v>0.78653800000000007</v>
       </c>
       <c r="J89" s="40">
         <f t="shared" si="28"/>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="K89" s="44">
         <f t="shared" si="29"/>
-        <v>1.3466079999999998</v>
+        <v>1.4529939999999999</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="G90" s="26">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>0.40523699999999996</v>
       </c>
       <c r="H90" s="39">
         <f t="shared" si="26"/>
@@ -9957,7 +9957,7 @@
       </c>
       <c r="I90" s="39">
         <f t="shared" si="27"/>
-        <v>1.088225</v>
+        <v>0.79894999999999994</v>
       </c>
       <c r="J90" s="40">
         <f t="shared" si="28"/>
@@ -9965,7 +9965,7 @@
       </c>
       <c r="K90" s="44">
         <f t="shared" si="29"/>
-        <v>1.3655299999999999</v>
+        <v>1.4814919999999998</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="G91" s="26">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>0.41972699999999996</v>
       </c>
       <c r="H91" s="39">
         <f t="shared" si="26"/>
@@ -9994,7 +9994,7 @@
       </c>
       <c r="I91" s="39">
         <f t="shared" si="27"/>
-        <v>1.10442</v>
+        <v>0.81083999999999989</v>
       </c>
       <c r="J91" s="40">
         <f t="shared" si="28"/>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="K91" s="44">
         <f t="shared" si="29"/>
-        <v>1.384182</v>
+        <v>1.5103289999999998</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="G92" s="26">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>0.42863100000000004</v>
       </c>
       <c r="H92" s="39">
         <f t="shared" si="26"/>
@@ -10031,7 +10031,7 @@
       </c>
       <c r="I92" s="39">
         <f t="shared" si="27"/>
-        <v>1.119272</v>
+        <v>0.82174400000000003</v>
       </c>
       <c r="J92" s="40">
         <f t="shared" si="28"/>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="K92" s="44">
         <f t="shared" si="29"/>
-        <v>1.401764</v>
+        <v>1.532867</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="G93" s="26">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>0.43856400000000001</v>
       </c>
       <c r="H93" s="39">
         <f t="shared" si="26"/>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="I93" s="39">
         <f t="shared" si="27"/>
-        <v>1.1332550000000001</v>
+        <v>0.83201000000000003</v>
       </c>
       <c r="J93" s="40">
         <f t="shared" si="28"/>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="K93" s="44">
         <f t="shared" si="29"/>
-        <v>1.4185610000000002</v>
+        <v>1.5558800000000002</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10097,7 +10097,7 @@
       </c>
       <c r="G94" s="26">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>0.44753100000000001</v>
       </c>
       <c r="H94" s="39">
         <f t="shared" si="26"/>
@@ -10105,7 +10105,7 @@
       </c>
       <c r="I94" s="39">
         <f t="shared" si="27"/>
-        <v>1.1454209999999998</v>
+        <v>0.84094199999999997</v>
       </c>
       <c r="J94" s="40">
         <f t="shared" si="28"/>
@@ -10113,7 +10113,7 @@
       </c>
       <c r="K94" s="44">
         <f t="shared" si="29"/>
-        <v>1.4334779999999998</v>
+        <v>1.57653</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="G95" s="26">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>0.45553200000000005</v>
       </c>
       <c r="H95" s="39">
         <f t="shared" si="26"/>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="I95" s="39">
         <f t="shared" si="27"/>
-        <v>1.156955</v>
+        <v>0.84940999999999989</v>
       </c>
       <c r="J95" s="40">
         <f t="shared" si="28"/>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="K95" s="44">
         <f t="shared" si="29"/>
-        <v>1.447721</v>
+        <v>1.5957080000000001</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="G96" s="12">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>0.46273500000000001</v>
       </c>
       <c r="H96" s="13">
         <f t="shared" si="26"/>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="I96" s="13">
         <f t="shared" si="27"/>
-        <v>1.167225</v>
+        <v>0.8569500000000001</v>
       </c>
       <c r="J96" s="14">
         <f t="shared" si="28"/>
@@ -10187,7 +10187,7 @@
       </c>
       <c r="K96" s="49">
         <f t="shared" si="29"/>
-        <v>1.4606159999999999</v>
+        <v>1.6130760000000002</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -10230,21 +10230,21 @@
     <row r="100" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="8" cm="1">
         <f t="array" ref="A100">INDEX(LINEST(K87:K96,A87:A96^{1,2}),1,1)</f>
-        <v>-3.7714015151515253E-8</v>
+        <v>-9.4215151515150488E-8</v>
       </c>
       <c r="B100" s="8" cm="1">
         <f t="array" ref="B100">INDEX(LINEST(K87:K96,A87:A96^{1,2}),1,2)</f>
-        <v>2.1118432575757592E-4</v>
+        <v>3.4988503030302943E-4</v>
       </c>
       <c r="C100" s="8" cm="1">
         <f t="array" ref="C100">INDEX(LINEST(K87:K96,A87:A96^{1,2}),1,3)</f>
-        <v>1.2880789166666664</v>
+        <v>1.3572238666666665</v>
       </c>
       <c r="D100" s="9"/>
       <c r="E100" s="6"/>
       <c r="F100" s="92">
         <f>$A$100*$A$3^2+$B$100*$A$3+$C$100</f>
-        <v>1.3842425757575756</v>
+        <v>1.5086125939393935</v>
       </c>
       <c r="G100" s="93"/>
       <c r="H100" s="94"/>

--- a/NuRePrCalc/ExcelDB.xlsx
+++ b/NuRePrCalc/ExcelDB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kursovaya\Kursach\NuRePrCalc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B304D7E-6C5D-48AB-AE85-60608C08EE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1258761E-4280-4D02-A30F-8B603E988499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7605" yWindow="2055" windowWidth="16065" windowHeight="12615" xr2:uid="{1CCBBA1E-2000-48FF-870F-B726FE87704F}"/>
   </bookViews>
